--- a/assets/raw-data/international-projects/international_projects.xlsx
+++ b/assets/raw-data/international-projects/international_projects.xlsx
@@ -1,22 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HesseE\mex-extractors\assets\raw-data\international-projects\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E81171-DD1F-4E2D-A1E6-7AC7E8118113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Introduction" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Projects" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Networks" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Introduction" sheetId="1" r:id="rId1"/>
+    <sheet name="Projects" sheetId="2" r:id="rId2"/>
+    <sheet name="Networks" sheetId="3" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Projects!$A$1:$T$9</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="_Hlk102055294" vbProcedure="false">projects!#ref!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Projects!$A$1:$T$9</definedName>
+    <definedName name="_Hlk102055294" localSheetId="1">Projects!#REF!</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -26,20 +34,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="82">
-  <si>
-    <t xml:space="preserve">This is a test document.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DROP-DOWN LISTS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project Abbreviation</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="79">
+  <si>
+    <t>This is a test document.</t>
+  </si>
+  <si>
+    <t>DROP-DOWN LISTS</t>
+  </si>
+  <si>
+    <t>Project Abbreviation</t>
   </si>
   <si>
     <r>
       <rPr>
-        <b val="true"/>
+        <b/>
         <sz val="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -49,280 +57,255 @@
     </r>
     <r>
       <rPr>
-        <i val="true"/>
+        <i/>
         <sz val="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(as in application or officially amended later)</t>
+      <t>(as in application or officially amended later)</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Start date DD.MM.YYYY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">End date DD.MM.YYYY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WHO region where project is active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partner countries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partner organizations (full name and acronym)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Activity 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Activity 2 (optional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Topic 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Topic 2 (optional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homepage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project lead (RKI unit)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project lead (person)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Additional RKI units involved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RKI internal project number (e.g. 1368-2022)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Funding type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Funding source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Funding programme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testAAbr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is a test project full title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bilateral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WHO AFRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test country</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laboratory diagnostics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FG99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roland Resolved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0000-1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Third party funded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test-Institute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testAAbr2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is a test project full title 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capacity building including trainings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public health systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">does not exist yet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FG18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0000-1001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GHPP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is a test project full title 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.12.2020 (31.08.2021)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consortium/multilateral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crisis management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0000-1002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testAAbr3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is a test project full title 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNICEF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-communicable diseases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0000-1003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testABR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-6 partner countries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conducting research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://test.de/en/projects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0000-1004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABRTEST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is a test project full title 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XX.XX.2019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XX.XX.2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0000-1005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TESTABR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is a test project full title 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XX.XX.2017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surveillance (infectious diseases)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.abc.org/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0000-1006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://yoyo.de/en/project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0000-1000TP09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GHPP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Host organisation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contact person RKI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit</t>
+    <t>Start date DD.MM.YYYY</t>
+  </si>
+  <si>
+    <t>End date DD.MM.YYYY</t>
+  </si>
+  <si>
+    <t>Project type</t>
+  </si>
+  <si>
+    <t>WHO region where project is active</t>
+  </si>
+  <si>
+    <t>Partner countries</t>
+  </si>
+  <si>
+    <t>Partner organizations (full name and acronym)</t>
+  </si>
+  <si>
+    <t>Activity 1</t>
+  </si>
+  <si>
+    <t>Activity 2 (optional)</t>
+  </si>
+  <si>
+    <t>Topic 1</t>
+  </si>
+  <si>
+    <t>Topic 2 (optional)</t>
+  </si>
+  <si>
+    <t>Homepage</t>
+  </si>
+  <si>
+    <t>Project lead (RKI unit)</t>
+  </si>
+  <si>
+    <t>Project lead (person)</t>
+  </si>
+  <si>
+    <t>Additional RKI units involved</t>
+  </si>
+  <si>
+    <t>RKI internal project number (e.g. 1368-2022)</t>
+  </si>
+  <si>
+    <t>Funding type</t>
+  </si>
+  <si>
+    <t>Funding source</t>
+  </si>
+  <si>
+    <t>Funding programme</t>
+  </si>
+  <si>
+    <t>testAAbr</t>
+  </si>
+  <si>
+    <t>This is a test project full title</t>
+  </si>
+  <si>
+    <t>Bilateral</t>
+  </si>
+  <si>
+    <t>WHO AFRO</t>
+  </si>
+  <si>
+    <t>Test country</t>
+  </si>
+  <si>
+    <t>WHO</t>
+  </si>
+  <si>
+    <t>Laboratory diagnostics</t>
+  </si>
+  <si>
+    <t>FG99</t>
+  </si>
+  <si>
+    <t>Roland Resolved</t>
+  </si>
+  <si>
+    <t>0000-1000</t>
+  </si>
+  <si>
+    <t>Third party funded</t>
+  </si>
+  <si>
+    <t>Test-Institute</t>
+  </si>
+  <si>
+    <t>testAAbr2</t>
+  </si>
+  <si>
+    <t>This is a test project full title 2</t>
+  </si>
+  <si>
+    <t>Capacity building including trainings</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Public health systems</t>
+  </si>
+  <si>
+    <t>does not exist yet</t>
+  </si>
+  <si>
+    <t>0000-1001</t>
+  </si>
+  <si>
+    <t>GHPP2</t>
+  </si>
+  <si>
+    <t>This is a test project full title 3</t>
+  </si>
+  <si>
+    <t>31.12.2020 (31.08.2021)</t>
+  </si>
+  <si>
+    <t>Consortium/multilateral</t>
+  </si>
+  <si>
+    <t>Crisis management</t>
+  </si>
+  <si>
+    <t>0000-1002</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>testAAbr3</t>
+  </si>
+  <si>
+    <t>This is a test project full title 4</t>
+  </si>
+  <si>
+    <t>UNICEF</t>
+  </si>
+  <si>
+    <t>Non-communicable diseases</t>
+  </si>
+  <si>
+    <t>0000-1003</t>
+  </si>
+  <si>
+    <t>testABR</t>
+  </si>
+  <si>
+    <t>2-6 partner countries</t>
+  </si>
+  <si>
+    <t>Conducting research</t>
+  </si>
+  <si>
+    <t>https://test.de/en/projects</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>0000-1004</t>
+  </si>
+  <si>
+    <t>ABRTEST</t>
+  </si>
+  <si>
+    <t>This is a test project full title 5</t>
+  </si>
+  <si>
+    <t>XX.XX.2019</t>
+  </si>
+  <si>
+    <t>XX.XX.2022</t>
+  </si>
+  <si>
+    <t>One Health</t>
+  </si>
+  <si>
+    <t>0000-1005</t>
+  </si>
+  <si>
+    <t>TESTABR</t>
+  </si>
+  <si>
+    <t>This is a test project full title 6</t>
+  </si>
+  <si>
+    <t>XX.XX.2017</t>
+  </si>
+  <si>
+    <t>Surveillance (infectious diseases)</t>
+  </si>
+  <si>
+    <t>https://www.abc.org/</t>
+  </si>
+  <si>
+    <t>0000-1006</t>
+  </si>
+  <si>
+    <t>ABR</t>
+  </si>
+  <si>
+    <t>https://yoyo.de/en/project</t>
+  </si>
+  <si>
+    <t>0000-1000TP09</t>
+  </si>
+  <si>
+    <t>GHPP1</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Host organisation</t>
+  </si>
+  <si>
+    <t>Contact person RKI</t>
+  </si>
+  <si>
+    <t>Unit</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
@@ -332,7 +315,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -340,7 +323,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -354,30 +337,36 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -398,13 +387,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.25"/>
+        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor rgb="FFB4C7E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.1"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor rgb="FFB4C7E7"/>
       </patternFill>
     </fill>
@@ -416,13 +405,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.5999"/>
+        <fgColor theme="4" tint="0.59987182226020086"/>
         <bgColor rgb="FF99CCFF"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -430,146 +419,66 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFAFABAB"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -628,64 +537,89 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="dropdownlisten"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -717,7 +651,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -741,7 +675,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -801,31 +735,30 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="11.4296875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="25.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="19.43"/>
+    <col min="1" max="1" width="50.54296875" customWidth="1"/>
+    <col min="2" max="2" width="44.81640625" customWidth="1"/>
+    <col min="3" max="3" width="19.1796875" customWidth="1"/>
+    <col min="4" max="4" width="25.08984375" customWidth="1"/>
+    <col min="5" max="5" width="20.453125" customWidth="1"/>
+    <col min="6" max="6" width="19.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:6" ht="150" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -835,7 +768,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -849,42 +782,34 @@
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T9"/>
-  <sheetFormatPr defaultColWidth="11.4296875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="21.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="40.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="5" width="15.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="4" width="22.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="4" width="15.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="4" width="25.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="4" width="40.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="4" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="4" width="25.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="4" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="4" width="25.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="16" style="4" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="4" width="22.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="4" width="20.57"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="21" style="4" width="11.43"/>
+    <col min="1" max="1" width="21.54296875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="40.54296875" style="4" customWidth="1"/>
+    <col min="3" max="4" width="15.54296875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="22.54296875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="15.54296875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="25.54296875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="40.54296875" style="4" customWidth="1"/>
+    <col min="9" max="12" width="20.54296875" style="4" customWidth="1"/>
+    <col min="13" max="13" width="25.54296875" style="4" customWidth="1"/>
+    <col min="14" max="14" width="20.54296875" style="4" customWidth="1"/>
+    <col min="15" max="15" width="25.54296875" style="4" customWidth="1"/>
+    <col min="16" max="18" width="20.54296875" style="4" customWidth="1"/>
+    <col min="19" max="19" width="22.54296875" style="4" customWidth="1"/>
+    <col min="20" max="20" width="20.54296875" style="4" customWidth="1"/>
+    <col min="21" max="16384" width="11.453125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="7" customFormat="true" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:20" s="7" customFormat="1" ht="26" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
@@ -946,17 +871,17 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" s="8" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:20" s="8" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>22</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="9" t="n">
+      <c r="C2" s="9">
         <v>44404</v>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="D2" s="10">
         <v>44561</v>
       </c>
       <c r="E2" s="8" t="s">
@@ -975,7 +900,7 @@
         <v>28</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="O2" s="8" t="s">
         <v>30</v>
@@ -993,17 +918,17 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" s="8" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:20" s="8" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="C3" s="9">
         <v>44927</v>
       </c>
-      <c r="D3" s="9" t="n">
+      <c r="D3" s="9">
         <v>46022</v>
       </c>
       <c r="E3" s="8" t="s">
@@ -1030,14 +955,14 @@
       <c r="M3" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="N3" s="8" t="s">
-        <v>40</v>
+      <c r="N3" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="O3" s="8" t="s">
         <v>30</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R3" s="8" t="s">
         <v>32</v>
@@ -1046,40 +971,40 @@
         <v>33</v>
       </c>
       <c r="T3" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="4" s="8" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:20" s="8" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
       <c r="B4" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="9">
+        <v>44075</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="9" t="n">
-        <v>44075</v>
-      </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="8" t="s">
         <v>44</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>45</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>25</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="N4" s="8" t="s">
-        <v>47</v>
+      <c r="N4" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="O4" s="8" t="s">
         <v>30</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="R4" s="8" t="s">
         <v>32</v>
@@ -1088,34 +1013,34 @@
         <v>33</v>
       </c>
       <c r="T4" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="5" s="12" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="9">
         <v>44409</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="10">
         <v>44926</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>25</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>36</v>
@@ -1124,10 +1049,13 @@
         <v>28</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="O5" s="8" t="s">
         <v>30</v>
@@ -1136,27 +1064,27 @@
         <v>29</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="S5" s="8" t="s">
         <v>33</v>
       </c>
       <c r="T5" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="6" s="8" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:20" s="8" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="C6" s="9">
         <v>44317</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="9">
         <v>45291</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>25</v>
@@ -1165,22 +1093,22 @@
         <v>26</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>38</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>59</v>
+        <v>56</v>
+      </c>
+      <c r="N6" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="O6" s="8" t="s">
         <v>30</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="R6" s="8" t="s">
         <v>32</v>
@@ -1189,39 +1117,39 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" s="8" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:20" s="8" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="D7" s="13" t="s">
         <v>62</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>64</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>25</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="L7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="N7" s="8" t="s">
-        <v>29</v>
+      <c r="N7" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="O7" s="8" t="s">
         <v>30</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="R7" s="8" t="s">
         <v>32</v>
@@ -1230,21 +1158,21 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" s="8" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:20" s="8" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="D8" s="13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>25</v>
@@ -1254,22 +1182,22 @@
       </c>
       <c r="H8" s="15"/>
       <c r="I8" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>28</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>72</v>
+        <v>69</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="O8" s="8" t="s">
         <v>30</v>
@@ -1278,7 +1206,7 @@
         <v>29</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="R8" s="8" t="s">
         <v>32</v>
@@ -1287,125 +1215,103 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" s="8" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:20" s="8" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="C9" s="9">
         <v>42370</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="10">
         <v>44926</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>25</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>29</v>
+        <v>72</v>
+      </c>
+      <c r="N9" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="O9" s="8" t="s">
         <v>30</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="R9" s="8" t="s">
         <v>32</v>
       </c>
       <c r="T9" s="8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T9"/>
-  <dataValidations count="8">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="I2:J2" type="list">
-      <formula1>#ref!</formula1>
+  <autoFilter ref="A1:T9" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:J2 R2:R9" xr:uid="{00000000-0002-0000-0100-000000000000}">
+      <formula1>#REF!</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="L2" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>$B$2:$B$7</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="R2:R9" type="list">
-      <formula1>#ref!</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="E2:E9" type="list">
-      <formula1>[international_projectsold.xlsx]dropdownlisten!#ref!</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K2:K8 L3:L8 K9:L9" type="list">
-      <formula1>[international_projectsold.xlsx]dropdownlisten!#ref!</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="F2:F9" type="list">
-      <formula1>[international_projectsold.xlsx]dropdownlisten!#ref!</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="I3:J9" type="list">
-      <formula1>[international_projectsold.xlsx]dropdownlisten!#ref!</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="T2:T9" type="list">
-      <formula1>[international_projectsold.xlsx]dropdownlisten!#ref!</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000003000000}">
+          <x14:formula1>
+            <xm:f>[international_projectsold.xlsx]dropdownlisten!#REF!</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>T2:T9 I3:J9 E2:F9 K2:K8 L3:L8 K9:L9</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="11.4296875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="16" width="75.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="30.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="30.57"/>
+    <col min="1" max="1" width="75.54296875" style="16" customWidth="1"/>
+    <col min="2" max="2" width="30.54296875" style="16" customWidth="1"/>
+    <col min="3" max="4" width="30.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="17"/>
     </row>
-    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="19" t="s">
         <v>78</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/assets/raw-data/international-projects/international_projects.xlsx
+++ b/assets/raw-data/international-projects/international_projects.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HesseE\mex-extractors\assets\raw-data\international-projects\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esinsj\code\mex-extractors\assets\raw-data\international-projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E81171-DD1F-4E2D-A1E6-7AC7E8118113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FDD3FE3-A519-4DBE-B998-D04F75781540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="5415" windowWidth="19185" windowHeight="11985" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,19 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Projects!$A$1:$T$9</definedName>
     <definedName name="_Hlk102055294" localSheetId="1">Projects!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -34,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="82">
   <si>
     <t>This is a test document.</t>
   </si>
@@ -290,6 +301,15 @@
   </si>
   <si>
     <t>Unit</t>
+  </si>
+  <si>
+    <t>FG18</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>C2</t>
   </si>
 </sst>
 </file>
@@ -424,9 +444,6 @@
   </cellStyleXfs>
   <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -473,6 +490,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -748,35 +768,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.54296875" customWidth="1"/>
-    <col min="2" max="2" width="44.81640625" customWidth="1"/>
-    <col min="3" max="3" width="19.1796875" customWidth="1"/>
-    <col min="4" max="4" width="25.08984375" customWidth="1"/>
-    <col min="5" max="5" width="20.453125" customWidth="1"/>
-    <col min="6" max="6" width="19.453125" customWidth="1"/>
+    <col min="1" max="1" width="50.5703125" customWidth="1"/>
+    <col min="2" max="2" width="44.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="4" max="4" width="25.140625" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
     </row>
-    <row r="3" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -790,463 +810,460 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.54296875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="40.54296875" style="4" customWidth="1"/>
-    <col min="3" max="4" width="15.54296875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="22.54296875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="15.54296875" style="4" customWidth="1"/>
-    <col min="7" max="7" width="25.54296875" style="4" customWidth="1"/>
-    <col min="8" max="8" width="40.54296875" style="4" customWidth="1"/>
-    <col min="9" max="12" width="20.54296875" style="4" customWidth="1"/>
-    <col min="13" max="13" width="25.54296875" style="4" customWidth="1"/>
-    <col min="14" max="14" width="20.54296875" style="4" customWidth="1"/>
-    <col min="15" max="15" width="25.54296875" style="4" customWidth="1"/>
-    <col min="16" max="18" width="20.54296875" style="4" customWidth="1"/>
-    <col min="19" max="19" width="22.54296875" style="4" customWidth="1"/>
-    <col min="20" max="20" width="20.54296875" style="4" customWidth="1"/>
-    <col min="21" max="16384" width="11.453125" style="4"/>
+    <col min="1" max="1" width="21.5703125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="40.5703125" style="3" customWidth="1"/>
+    <col min="3" max="4" width="15.5703125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="22.5703125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="25.5703125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="40.5703125" style="3" customWidth="1"/>
+    <col min="9" max="12" width="20.5703125" style="3" customWidth="1"/>
+    <col min="13" max="13" width="25.5703125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="20.5703125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="25.5703125" style="3" customWidth="1"/>
+    <col min="16" max="18" width="20.5703125" style="3" customWidth="1"/>
+    <col min="19" max="19" width="22.5703125" style="3" customWidth="1"/>
+    <col min="20" max="20" width="20.5703125" style="3" customWidth="1"/>
+    <col min="21" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="7" customFormat="1" ht="26" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:20" s="6" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="S1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="8" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:20" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="8">
         <v>44404</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="9">
         <v>44561</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="8">
+        <v>44927</v>
+      </c>
+      <c r="D3" s="8">
+        <v>46022</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="S3" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T3" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="11"/>
+      <c r="B4" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="8">
+        <v>44075</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="8">
+        <v>44409</v>
+      </c>
+      <c r="D5" s="9">
+        <v>44926</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="S5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T5" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="8">
+        <v>44317</v>
+      </c>
+      <c r="D6" s="8">
+        <v>45291</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="N6" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="O6" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="Q6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="R6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="S6" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="N7" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="Q2" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="R2" s="8" t="s">
+      <c r="O7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="R7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="S2" s="8" t="s">
-        <v>33</v>
+      <c r="T7" s="7" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:20" s="8" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="9">
-        <v>44927</v>
-      </c>
-      <c r="D3" s="9">
-        <v>46022</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="8" t="s">
+    <row r="8" spans="1:20" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G8" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" s="8" t="s">
+      <c r="H8" s="14"/>
+      <c r="I8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="R8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N3" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="O3" s="8" t="s">
+    </row>
+    <row r="9" spans="1:20" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="8">
+        <v>42370</v>
+      </c>
+      <c r="D9" s="9">
+        <v>44926</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="N9" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="O9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="Q3" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="R3" s="8" t="s">
+      <c r="Q9" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="R9" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="S3" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="T3" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" s="8" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="12"/>
-      <c r="B4" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="9">
-        <v>44075</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="N4" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="S4" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="T4" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="9">
-        <v>44409</v>
-      </c>
-      <c r="D5" s="10">
-        <v>44926</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="N5" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="S5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="T5" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" s="8" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="9">
-        <v>44317</v>
-      </c>
-      <c r="D6" s="9">
-        <v>45291</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q6" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="R6" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="S6" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" s="8" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q7" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="R7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="T7" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" s="8" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="15"/>
-      <c r="I8" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="N8" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="O8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="R8" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="T8" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" s="8" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="9">
-        <v>42370</v>
-      </c>
-      <c r="D9" s="10">
-        <v>44926</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="N9" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="O9" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q9" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="R9" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="T9" s="8" t="s">
+      <c r="T9" s="7" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1286,27 +1303,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="75.54296875" style="16" customWidth="1"/>
-    <col min="2" max="2" width="30.54296875" style="16" customWidth="1"/>
-    <col min="3" max="4" width="30.54296875" customWidth="1"/>
+    <col min="1" max="1" width="75.5703125" style="15" customWidth="1"/>
+    <col min="2" max="2" width="30.5703125" style="15" customWidth="1"/>
+    <col min="3" max="4" width="30.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="17"/>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="16"/>
     </row>
-    <row r="2" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>78</v>
       </c>
     </row>
